--- a/artfynd/A 7702-2025 artfynd.xlsx
+++ b/artfynd/A 7702-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115991331</v>
+        <v>115991332</v>
       </c>
       <c r="B2" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115991332</v>
+        <v>115991331</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
